--- a/output/2026-10-05_04_Malesia_Terengganu_Componentistica_Ventilazione_industriale.xlsx
+++ b/output/2026-10-05_04_Malesia_Terengganu_Componentistica_Ventilazione_industriale.xlsx
@@ -489,8 +489,6 @@
           <t>Componentistica / Ventilazione industriale</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>Filiale fisica confermata: K-428, Ground Floor, Taman Kemaman, 24000 Kemaman, Terengganu (fonte: pagina ufficiale ERIKS + riscontri indipendenti). Distributore tecnico multinazionale (trasmissioni di potenza, ventilatori/soffianti industriali, guarnizioni, tubi flessibili, tenute). Telefono/email specifici non reperiti con fonte attendibile.</t>
@@ -498,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -535,7 +533,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Marketplace/distributore B2B MRO con servizio logistico confermato per Kuala Terengganu e Kemaman (supply base oil&amp;gas). Catalogo generale include categoria 'Industrial Equipment - Fans' con consegna nazionale. RISERVA: le pagine regionali dedicate a Kemaman/Kuala Terengganu non citano esplicitamente i ventilatori tra le categorie regionali; pertinenza al settore ventilazione supportata dal catalogo nazionale generale, non da pagina regionale dedicata.</t>
+          <t>Marketplace/distributore B2B MRO con servizio logistico confermato per Kuala Terengganu e Kemaman (supply base oil&amp;gas). Catalogo generale include categoria 'Industrial Equipment - Fans' con consegna nazionale. RISERVA: le pagine regionali dedicate a Kemaman/Kuala Terengganu non citano esplicitamente i ventilatori tra le categorie regionali; pertinenza al settore ventilazione supportata dal catalogo nazionale generale, non da pagina regionale dedicata. [DUPLICATO — vedi anche: 2026-10-02_19_Malesia_Negeri_Sembilan_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
